--- a/specs/008-bf2marc-v3.1.xlsx
+++ b/specs/008-bf2marc-v3.1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\share\BF to MARC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{166EC96D-8447-4250-9569-BB53E36265EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AABB9C59-2832-4AAA-A1B3-0001ACAA67D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="380" windowWidth="14380" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -363,9 +363,6 @@
     <t>W - supplementaryContent - SupplementaryContent - http://id.loc.gov/vocabularly/msupplecont/&lt;code&gt;</t>
   </si>
   <si>
-    <t>mapping: "gf2014026339"="1"; "gf2014026339"="1"; "gf2014026094"="1"; "gf2015026020"="1"; "gf2014026110"="1"; "gf2014026141"="1"; "gf2014026542"="1"; "gf2014026481"="1"; "gf2011026363"="1" ; default = "0"</t>
-  </si>
-  <si>
     <t xml:space="preserve">  IF fontSize - FontSize or notation - TactileNotation do not exist, THEN I - carrier - Carrier - http://id.loc.gov/vocabulary/carriers/&lt;code&gt;</t>
   </si>
   <si>
@@ -477,14 +474,17 @@
     <t>default = "|"</t>
   </si>
   <si>
-    <t>008 field construction by format, v3.1, 12/02/2025</t>
+    <t>008 field construction by format, v3.1, 03/05/2026</t>
+  </si>
+  <si>
+    <t>mapping: "gf2014026339"="1"; "gf2014026297"="d" ; "gf2014026094"="e"; "gf2015026020"="f"; "gf2014026110"="h"; "gf2014026141"="i"; "gf2014026542"="j"; "gf2014026481"="p"; "gf2011026363"="s" ; default = "0"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -533,6 +533,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -569,7 +576,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -603,6 +610,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -896,7 +906,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
@@ -960,7 +970,7 @@
         <v>92</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="31" x14ac:dyDescent="0.35">
@@ -971,90 +981,90 @@
         <v>93</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="9" customFormat="1" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A10" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>131</v>
-      </c>
       <c r="C10" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D10" s="8"/>
     </row>
     <row r="11" spans="1:5" s="9" customFormat="1" ht="31" x14ac:dyDescent="0.35">
       <c r="A11" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B11" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="C11" s="8" t="s">
         <v>133</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>134</v>
       </c>
       <c r="D11" s="8"/>
     </row>
     <row r="12" spans="1:5" s="9" customFormat="1" ht="31" x14ac:dyDescent="0.35">
       <c r="A12" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>136</v>
-      </c>
       <c r="C12" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D12" s="8"/>
     </row>
     <row r="13" spans="1:5" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A13" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>138</v>
-      </c>
       <c r="C13" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D13" s="8"/>
     </row>
     <row r="14" spans="1:5" s="9" customFormat="1" ht="31" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>140</v>
-      </c>
       <c r="C14" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D14" s="8"/>
     </row>
     <row r="15" spans="1:5" s="9" customFormat="1" ht="31" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>148</v>
-      </c>
       <c r="C15" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D15" s="8"/>
     </row>
     <row r="16" spans="1:5" s="9" customFormat="1" ht="31" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D16" s="8"/>
     </row>
@@ -1077,7 +1087,7 @@
         <v>11</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -1093,13 +1103,13 @@
     </row>
     <row r="20" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B20" s="9" t="s">
         <v>13</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D20" s="8"/>
     </row>
@@ -1148,13 +1158,13 @@
     </row>
     <row r="27" spans="1:4" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="28" spans="1:4" s="9" customFormat="1" ht="46.5" x14ac:dyDescent="0.35">
@@ -1165,7 +1175,7 @@
         <v>25</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D28" s="8"/>
     </row>
@@ -1177,7 +1187,7 @@
         <v>25</v>
       </c>
       <c r="C29" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D29" s="8"/>
     </row>
@@ -1233,15 +1243,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="77.5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" ht="62" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>102</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>112</v>
+      <c r="C35" s="12" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="31" x14ac:dyDescent="0.35">
@@ -1281,13 +1291,13 @@
     </row>
     <row r="41" spans="1:3" ht="31" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
@@ -1343,7 +1353,7 @@
     </row>
     <row r="49" spans="1:3" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A49" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>17</v>
@@ -1403,7 +1413,7 @@
         <v>20</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="56" spans="1:3" ht="31" x14ac:dyDescent="0.35">
@@ -1411,18 +1421,18 @@
         <v>22</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
@@ -1527,13 +1537,13 @@
     </row>
     <row r="70" spans="1:3" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A70" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="71" spans="1:3" ht="93" x14ac:dyDescent="0.35">
@@ -1544,18 +1554,18 @@
         <v>59</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="186" x14ac:dyDescent="0.35">
       <c r="A72" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B72" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>121</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
@@ -1634,7 +1644,7 @@
         <v>19</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D82" s="10"/>
     </row>
@@ -1660,13 +1670,13 @@
     </row>
     <row r="85" spans="1:4" s="11" customFormat="1" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A85" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D85" s="10"/>
     </row>
@@ -1689,7 +1699,7 @@
         <v>65</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D87" s="8"/>
     </row>
@@ -1701,7 +1711,7 @@
         <v>25</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D88" s="8"/>
     </row>
@@ -1816,7 +1826,7 @@
         <v>20</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="31" x14ac:dyDescent="0.35">
@@ -1824,18 +1834,18 @@
         <v>22</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A103" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>30</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.35">
@@ -1848,13 +1858,13 @@
     </row>
     <row r="105" spans="1:3" ht="310" x14ac:dyDescent="0.35">
       <c r="A105" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>33</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="46.5" x14ac:dyDescent="0.35">
@@ -1899,13 +1909,13 @@
     </row>
     <row r="112" spans="1:3" ht="46.5" x14ac:dyDescent="0.35">
       <c r="A112" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>23</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.35">
